--- a/StructureDefinition-checked-in-participant.xlsx
+++ b/StructureDefinition-checked-in-participant.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/checked-in-participant</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/checked-in-participant</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T13:18:28+00:00</t>
+    <t>2026-10-29T07:06:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>affiliation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/affiliation}
+    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/affiliation}
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>primaryTrack</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/primary-track}
+    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/primary-track}
 </t>
   </si>
   <si>
@@ -668,7 +668,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/identifier/participant-2026</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/identifier/participant-2026</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1434,7 +1434,7 @@
     <t>Practitioner.qualification:eventRole.code</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/ValueSet/participation-roles</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/ValueSet/participation-roles</t>
   </si>
   <si>
     <t>Practitioner.qualification:eventRole.code.id</t>
@@ -1510,7 +1510,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/CodeSystem/participation-role</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/CodeSystem/participation-role</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1990,7 +1990,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="85.00390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2005,7 +2005,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.4609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.4453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.4453125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-checked-in-participant.xlsx
+++ b/StructureDefinition-checked-in-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:06:30+00:00</t>
+    <t>2026-10-29T08:26:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-checked-in-participant.xlsx
+++ b/StructureDefinition-checked-in-participant.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:26:45+00:00</t>
+    <t>2026-10-29T09:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-checked-in-participant.xlsx
+++ b/StructureDefinition-checked-in-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:23:29+00:00</t>
+    <t>2026-10-29T13:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-checked-in-participant.xlsx
+++ b/StructureDefinition-checked-in-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:05:39+00:00</t>
+    <t>2026-10-29T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-checked-in-participant.xlsx
+++ b/StructureDefinition-checked-in-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T15:50:41+00:00</t>
+    <t>2026-10-29T16:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-checked-in-participant.xlsx
+++ b/StructureDefinition-checked-in-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T16:44:10+00:00</t>
+    <t>2026-10-30T09:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
